--- a/archive/InnovateUK_Funding_Opportunities_Latest_2026-04-29.xlsx
+++ b/archive/InnovateUK_Funding_Opportunities_Latest_2026-04-29.xlsx
@@ -1377,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1450,6 +1450,118 @@
         <is>
           <t>Week commencing (Wed)</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Dual-use aviation systems and autonomy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/dual-use-aviation-systems-and-autonomy/</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:22</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>46141.47361111111</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="b">
+        <v>0</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>03/06/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>£10.0 million</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="n">
+        <v>46141</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Innovate UK Business Connect</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Counter UAS (Uncrewed Aerial Systems) Technologies</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://iuk-business-connect.org.uk/opportunities/counter-uas-uncrewed-aerial-systems-technologies/</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2026-04-29 11:22</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46141.47361111111</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>03/06/2026                              11:00</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="n">
+        <v>46141</v>
       </c>
     </row>
   </sheetData>
@@ -1463,7 +1575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D47"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1490,329 +1602,329 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>46134</v>
+        <v>46141</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>46127</v>
+        <v>46134</v>
       </c>
       <c r="B3" t="n">
         <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>46120</v>
+        <v>46127</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>46113</v>
+        <v>46120</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>46106</v>
+        <v>46113</v>
       </c>
       <c r="B6" t="n">
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>46099</v>
+        <v>46106</v>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>46092</v>
+        <v>46099</v>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>46085</v>
+        <v>46092</v>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>46078</v>
+        <v>46085</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>46071</v>
+        <v>46078</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>46064</v>
+        <v>46071</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D12" t="n">
         <v>9</v>
-      </c>
-      <c r="D12" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>46057</v>
+        <v>46064</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>46050</v>
+        <v>46057</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46043</v>
+        <v>46050</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46036</v>
+        <v>46043</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46029</v>
+        <v>46036</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46022</v>
+        <v>46029</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46015</v>
+        <v>46022</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46008</v>
+        <v>46015</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46001</v>
+        <v>46008</v>
       </c>
       <c r="B21" t="n">
         <v>2</v>
       </c>
       <c r="C21" t="n">
-        <v>77</v>
+        <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>79</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>45994</v>
+        <v>46001</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>45987</v>
+        <v>45994</v>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>45980</v>
+        <v>45987</v>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>45973</v>
+        <v>45980</v>
       </c>
       <c r="B25" t="n">
         <v>0</v>
@@ -1826,91 +1938,91 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>45966</v>
+        <v>45973</v>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>45959</v>
+        <v>45966</v>
       </c>
       <c r="B27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>45952</v>
+        <v>45959</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>45945</v>
+        <v>45952</v>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>45938</v>
+        <v>45945</v>
       </c>
       <c r="B30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C30" t="n">
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>45931</v>
+        <v>45938</v>
       </c>
       <c r="B31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>45924</v>
+        <v>45931</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -1924,35 +2036,35 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>45917</v>
+        <v>45924</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C33" t="n">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>45910</v>
+        <v>45917</v>
       </c>
       <c r="B34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>45903</v>
+        <v>45910</v>
       </c>
       <c r="B35" t="n">
         <v>2</v>
@@ -1966,169 +2078,183 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>45896</v>
+        <v>45903</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>45889</v>
+        <v>45896</v>
       </c>
       <c r="B37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>45882</v>
+        <v>45889</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>45875</v>
+        <v>45882</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>45868</v>
+        <v>45875</v>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>45861</v>
+        <v>45868</v>
       </c>
       <c r="B41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>45854</v>
+        <v>45861</v>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>45847</v>
+        <v>45854</v>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>45840</v>
+        <v>45847</v>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>45833</v>
+        <v>45840</v>
       </c>
       <c r="B45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>45826</v>
+        <v>45833</v>
       </c>
       <c r="B46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C46" t="n">
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
+        <v>45826</v>
+      </c>
+      <c r="B47" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
         <v>45819</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" t="n">
         <v>25</v>
       </c>
-      <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="n">
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" t="n">
         <v>25</v>
       </c>
     </row>
@@ -2143,7 +2269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N379"/>
+  <dimension ref="A1:N381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14473,26 +14599,26 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
+          <t>Dual-use aviation systems and autonomy</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/dual-use-aviation-systems-and-autonomy/</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-04-29 11:22</t>
         </is>
       </c>
       <c r="E238" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46141.47361111111</v>
       </c>
       <c r="F238" t="b">
         <v>1</v>
@@ -14501,48 +14627,54 @@
       <c r="H238" t="b">
         <v>0</v>
       </c>
-      <c r="I238" t="inlineStr"/>
-      <c r="J238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J238" s="1" t="n">
+        <v>46147</v>
+      </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>03/06/2026                              11:00</t>
         </is>
       </c>
       <c r="L238" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N238" s="1" t="n">
-        <v>45819</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Innovate Funding Service</t>
+          <t>Innovate UK Business Connect</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 2</t>
+          <t>Counter UAS (Uncrewed Aerial Systems) Technologies</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
+          <t>https://iuk-business-connect.org.uk/opportunities/counter-uas-uncrewed-aerial-systems-technologies/</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2025-06-14 08:41</t>
+          <t>2026-04-29 11:22</t>
         </is>
       </c>
       <c r="E239" s="1" t="n">
-        <v>45822.36180555556</v>
+        <v>46141.47361111111</v>
       </c>
       <c r="F239" t="b">
         <v>1</v>
@@ -14551,23 +14683,29 @@
       <c r="H239" t="b">
         <v>0</v>
       </c>
-      <c r="I239" t="inlineStr"/>
-      <c r="J239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="J239" s="1" t="n">
+        <v>46147</v>
+      </c>
       <c r="K239" t="inlineStr">
         <is>
-          <t>Thursday 24 July 2025 11:00am</t>
+          <t>03/06/2026                              11:00</t>
         </is>
       </c>
       <c r="L239" s="1" t="n">
-        <v>45862.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N239" s="1" t="n">
-        <v>45819</v>
+        <v>46141</v>
       </c>
     </row>
     <row r="240">
@@ -14578,12 +14716,12 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
+          <t>Future Leaders Fellowships: Round 10, business and non-academic</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2058/overview/0f904547-f415-4fb9-94a7-0701c38a2ba1</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -14605,15 +14743,15 @@
       <c r="J240" t="inlineStr"/>
       <c r="K240" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L240" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N240" s="1" t="n">
@@ -14628,12 +14766,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>New Innovators in Marine and Maritime, Great South West</t>
+          <t>ADOPT Facilitator Support Grant: Round 2</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2223/overview/4e423e05-3228-45e3-9cfe-0b39d1227307</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14655,15 +14793,15 @@
       <c r="J241" t="inlineStr"/>
       <c r="K241" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 24 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L241" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45862.45833333334</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N241" s="1" t="n">
@@ -14678,12 +14816,12 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
+          <t>MSI Improving energy or resource efficiency in manufacturing FS</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2225/overview/c43ef163-3872-4178-b80d-88c406691610</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -14705,15 +14843,15 @@
       <c r="J242" t="inlineStr"/>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Thursday 4 September 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L242" s="1" t="n">
-        <v>45904.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N242" s="1" t="n">
@@ -14728,12 +14866,12 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – June 2025</t>
+          <t>New Innovators in Marine and Maritime, Great South West</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2215/overview/67b86d6c-bab9-4a01-aacc-3da2e57edc99</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -14755,13 +14893,17 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L243" s="1" t="n">
-        <v>45826.45833333334</v>
-      </c>
-      <c r="M243" t="inlineStr"/>
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>£50,000</t>
+        </is>
+      </c>
       <c r="N243" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14774,12 +14916,12 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Defra Farming Innovation Investor Partnership</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Autumn</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2217/overview/c555f64e-5485-4e49-89b8-32d61fac4ff0</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -14801,15 +14943,15 @@
       <c r="J244" t="inlineStr"/>
       <c r="K244" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Thursday 4 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L244" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45904.45833333334</v>
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N244" s="1" t="n">
@@ -14824,12 +14966,12 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
+          <t>ATI Programme strategic batch: EoI – June 2025</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2218/overview/a45dcc8a-b621-4a79-9e4d-046e19b6b1e9</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14851,17 +14993,13 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L245" s="1" t="n">
-        <v>45833.45833333334</v>
-      </c>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45826.45833333334</v>
+      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="N245" s="1" t="n">
         <v>45819</v>
       </c>
@@ -14874,12 +15012,12 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
+          <t>Defra Farming Innovation Investor Partnership</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2207/overview/05e5263b-75a1-49a0-87f0-261541af0840</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14901,15 +15039,15 @@
       <c r="J246" t="inlineStr"/>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L246" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N246" s="1" t="n">
@@ -14924,12 +15062,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C3</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2204/overview/9da241b9-1fd8-49fb-b8d0-4a81a637b3b5</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -14951,15 +15089,15 @@
       <c r="J247" t="inlineStr"/>
       <c r="K247" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L247" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N247" s="1" t="n">
@@ -14974,12 +15112,12 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
+          <t>Ofgem Strategic Innovation Fund Round 4 Discovery C3</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2200/overview/0f0721c8-5a37-4046-8e4f-7649194e8adc</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -15001,15 +15139,15 @@
       <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L248" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N248" s="1" t="n">
@@ -15024,12 +15162,12 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
+          <t>Contracts for Innovation: Scaling community initiatives in diet and exercise</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2191/overview/6a097cf8-8f81-495d-b56f-3f240cfde64c</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15051,15 +15189,15 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L249" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N249" s="1" t="n">
@@ -15074,12 +15212,12 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Clean Air, Phase 3</t>
+          <t>Contracts for Innovation: Quantum Sensors and PNT Missions Primer</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2209/overview/28f8801b-a8b3-48c8-8c81-64d75341b81d</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15101,15 +15239,15 @@
       <c r="J250" t="inlineStr"/>
       <c r="K250" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L250" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N250" s="1" t="n">
@@ -15124,12 +15262,12 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
+          <t>Contracts for Innovation: Net Zero Living Tech Trials, phase 3</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2189/overview/a59ac38e-662b-49a5-b7f9-a44c2cc38c61</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -15151,15 +15289,15 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L251" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N251" s="1" t="n">
@@ -15174,12 +15312,12 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
+          <t>Contracts for Innovation: Clean Air, Phase 3</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2181/overview/02aad9d2-c984-4bd5-a3f6-80f25ec62870</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -15201,15 +15339,15 @@
       <c r="J252" t="inlineStr"/>
       <c r="K252" t="inlineStr">
         <is>
-          <t>Wednesday 18 June 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L252" s="1" t="n">
-        <v>45826.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N252" s="1" t="n">
@@ -15224,12 +15362,12 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Canada-UK Semiconductors</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI Tools and software</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2194/overview/91c68630-20eb-4247-8296-ae1737637756</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -15251,15 +15389,15 @@
       <c r="J253" t="inlineStr"/>
       <c r="K253" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L253" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N253" s="1" t="n">
@@ -15274,12 +15412,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
+          <t>Contracts for Innovation: DSbD Advancing CHERI RISC-V Devices</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2198/overview/b2e2fd41-d372-4e33-a6df-8bfefb8de0f9</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15301,15 +15439,15 @@
       <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 18 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L254" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45826.45833333334</v>
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>£35,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N254" s="1" t="n">
@@ -15324,12 +15462,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Innovate UK innovation loans future economy: Round 21</t>
+          <t>Canada-UK Semiconductors</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2192/overview/3906cbd5-fec2-4c1f-897d-ccab071708b3</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15351,15 +15489,15 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L255" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N255" s="1" t="n">
@@ -15374,12 +15512,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
+          <t>Accelerated Knowledge Transfer 4 (AKT4) Addiction</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2178/overview/2699060f-dd6f-415b-ae47-bead15aa430e</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -15401,15 +15539,15 @@
       <c r="J256" t="inlineStr"/>
       <c r="K256" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L256" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£35,000</t>
         </is>
       </c>
       <c r="N256" s="1" t="n">
@@ -15424,12 +15562,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
+          <t>Innovate UK innovation loans future economy: Round 21</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2188/overview/20c89a26-2479-4f80-b35a-b62ed3b9b3ce</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15451,15 +15589,15 @@
       <c r="J257" t="inlineStr"/>
       <c r="K257" t="inlineStr">
         <is>
-          <t>Wednesday 25 June 2025 11:00am</t>
+          <t>Wednesday 2 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L257" s="1" t="n">
-        <v>45833.45833333334</v>
+        <v>45840.45833333334</v>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>£2.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N257" s="1" t="n">
@@ -15474,12 +15612,12 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
+          <t>Farming Futures R&amp;D Fund: Precision Breeding Competition</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2168/overview/0fef9171-75b0-4f3e-acef-42920e7e5d5e</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -15501,15 +15639,15 @@
       <c r="J258" t="inlineStr"/>
       <c r="K258" t="inlineStr">
         <is>
-          <t>Wednesday 2 July 2025 11:00am</t>
+          <t>Wednesday 25 June 2025 11:00am</t>
         </is>
       </c>
       <c r="L258" s="1" t="n">
-        <v>45840.45833333334</v>
+        <v>45833.45833333334</v>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N258" s="1" t="n">
@@ -15524,12 +15662,12 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 1</t>
+          <t>Farming Futures R&amp;D Fund: low emissions farming</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2169/overview/64b0d550-3f46-4ab4-a0cd-5fa7ac488cb6</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -15559,7 +15697,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.5 million</t>
         </is>
       </c>
       <c r="N259" s="1" t="n">
@@ -15574,12 +15712,12 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
+          <t>Investor Partnerships: Clean Energy and Climate Technologies</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2175/overview/7487b4f1-51e6-4f15-a4c8-f103559d14bb</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15601,11 +15739,17 @@
       <c r="J260" t="inlineStr"/>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
+          <t>Wednesday 2 July 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L260" s="1" t="n">
+        <v>45840.45833333334</v>
+      </c>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>£2.0 million</t>
+        </is>
+      </c>
       <c r="N260" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15618,12 +15762,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Horizon Europe Guarantee Extension</t>
+          <t>Full ADOPT Grant: Round 1</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2162/overview/c35de0a9-5072-4142-8a52-1cdce8ef3871</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15645,11 +15789,17 @@
       <c r="J261" t="inlineStr"/>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Thursday 27 November 2025 4:00pm</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
+          <t>Wednesday 25 June 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L261" s="1" t="n">
+        <v>45833.45833333334</v>
+      </c>
+      <c r="M261" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N261" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15662,21 +15812,21 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
+          <t>Horizon Europe Guarantee - EIT KICs 2023</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1585/overview/32135a71-171a-46bf-ad56-e2e65a1a3574</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025-06-16 22:04</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E262" s="1" t="n">
-        <v>45824.91944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F262" t="b">
         <v>1</v>
@@ -15689,17 +15839,11 @@
       <c r="J262" t="inlineStr"/>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L262" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M262" t="inlineStr">
-        <is>
-          <t>£8,500</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr"/>
+      <c r="M262" t="inlineStr"/>
       <c r="N262" s="1" t="n">
         <v>45819</v>
       </c>
@@ -15712,21 +15856,21 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
+          <t>Horizon Europe Guarantee Extension</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/1389/overview/b900fdc4-c48d-4d8a-8733-ce4ca210ae9a</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-14 08:41</t>
         </is>
       </c>
       <c r="E263" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45822.36180555556</v>
       </c>
       <c r="F263" t="b">
         <v>1</v>
@@ -15739,19 +15883,13 @@
       <c r="J263" t="inlineStr"/>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L263" s="1" t="n">
-        <v>45889.45833333334</v>
-      </c>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>£500,000</t>
-        </is>
-      </c>
+          <t>Thursday 27 November 2025 4:00pm</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr"/>
+      <c r="M263" t="inlineStr"/>
       <c r="N263" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="264">
@@ -15762,21 +15900,21 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 2</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 3</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2184/overview/c599b17c-e13a-4e13-995e-53cc4d4508a1</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2025-06-26 08:52</t>
+          <t>2025-06-16 22:04</t>
         </is>
       </c>
       <c r="E264" s="1" t="n">
-        <v>45834.36944444444</v>
+        <v>45824.91944444444</v>
       </c>
       <c r="F264" t="b">
         <v>1</v>
@@ -15789,19 +15927,19 @@
       <c r="J264" t="inlineStr"/>
       <c r="K264" t="inlineStr">
         <is>
-          <t>Wednesday 20 August 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L264" s="1" t="n">
-        <v>45889.45833333334</v>
+        <v>45917.45833333334</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N264" s="1" t="n">
-        <v>45833</v>
+        <v>45819</v>
       </c>
     </row>
     <row r="265">
@@ -15812,21 +15950,21 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 22</t>
+          <t>Agri-tech and food technology, Mid and North Wales - CRD</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2212/overview/4411087f-2a92-4aed-b735-d1a813376bec</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2025-07-03 08:52</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E265" s="1" t="n">
-        <v>45841.36944444444</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F265" t="b">
         <v>1</v>
@@ -15839,19 +15977,19 @@
       <c r="J265" t="inlineStr"/>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L265" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N265" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="266">
@@ -15862,21 +16000,21 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Growth Catalyst Early Stage: New Innovators</t>
+          <t>Full ADOPT Grant Round 2</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2222/overview/c3d5b2f9-e4d4-4ddc-99a2-589904ac3d42</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-06-26 08:52</t>
         </is>
       </c>
       <c r="E266" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45834.36944444444</v>
       </c>
       <c r="F266" t="b">
         <v>1</v>
@@ -15889,19 +16027,19 @@
       <c r="J266" t="inlineStr"/>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Wednesday 6 August 2025 11:00am</t>
+          <t>Wednesday 20 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L266" s="1" t="n">
-        <v>45875.45833333334</v>
+        <v>45889.45833333334</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N266" s="1" t="n">
-        <v>45840</v>
+        <v>45833</v>
       </c>
     </row>
     <row r="267">
@@ -15912,21 +16050,21 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – July 2025</t>
+          <t>Innovate UK Innovation Loans Round 22</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2236/overview/70cbae59-4e67-4626-8cb0-6bbbfc0cf6b7</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2025-07-07 08:54</t>
+          <t>2025-07-03 08:52</t>
         </is>
       </c>
       <c r="E267" s="1" t="n">
-        <v>45845.37083333333</v>
+        <v>45841.36944444444</v>
       </c>
       <c r="F267" t="b">
         <v>1</v>
@@ -15939,13 +16077,17 @@
       <c r="J267" t="inlineStr"/>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Wednesday 23 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L267" s="1" t="n">
-        <v>45861.45833333334</v>
-      </c>
-      <c r="M267" t="inlineStr"/>
+        <v>45896.45833333334</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>£5.0 million</t>
+        </is>
+      </c>
       <c r="N267" s="1" t="n">
         <v>45840</v>
       </c>
@@ -15958,21 +16100,21 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
+          <t>Growth Catalyst Early Stage: New Innovators</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2220/overview/bcfd2780-f307-4434-be32-46889a239024</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E268" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F268" t="b">
         <v>1</v>
@@ -15985,19 +16127,19 @@
       <c r="J268" t="inlineStr"/>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 6 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L268" s="1" t="n">
-        <v>45896.45833333334</v>
+        <v>45875.45833333334</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N268" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="269">
@@ -16008,21 +16150,21 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
+          <t>ATI Programme strategic batch: EoI – July 2025</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2228/overview/5ccf059d-ae66-4f72-a319-4b12cbd46d1c</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2025-07-09 08:54</t>
+          <t>2025-07-07 08:54</t>
         </is>
       </c>
       <c r="E269" s="1" t="n">
-        <v>45847.37083333333</v>
+        <v>45845.37083333333</v>
       </c>
       <c r="F269" t="b">
         <v>1</v>
@@ -16035,19 +16177,15 @@
       <c r="J269" t="inlineStr"/>
       <c r="K269" t="inlineStr">
         <is>
-          <t>Wednesday 27 August 2025 11:00am</t>
+          <t>Wednesday 23 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L269" s="1" t="n">
-        <v>45896.45833333334</v>
-      </c>
-      <c r="M269" t="inlineStr">
-        <is>
-          <t>£300,000</t>
-        </is>
-      </c>
+        <v>45861.45833333334</v>
+      </c>
+      <c r="M269" t="inlineStr"/>
       <c r="N269" s="1" t="n">
-        <v>45847</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="270">
@@ -16058,12 +16196,12 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
+          <t>Contracts for Innovation: Resource Efficient Construction Impacts</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2242/overview/51b1338a-0d60-43de-b062-fe7a48a7d42f</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -16108,12 +16246,12 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Future Flight: Regional Demonstrator 2</t>
+          <t>Contracts for Innovation: Resource Efficient Chemicals Impacts</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2240/overview/10f28eca-01f0-4abf-8e0c-998151fe747b</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -16135,15 +16273,15 @@
       <c r="J271" t="inlineStr"/>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Thursday 17 July 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L271" s="1" t="n">
-        <v>45855.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N271" s="1" t="n">
@@ -16158,21 +16296,21 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies</t>
+          <t>Contracts for Innovation: Resource Efficient Automotive Impacts</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2241/overview/baec7aff-ca8b-456c-9e4d-d6eb9621a988</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E272" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F272" t="b">
         <v>1</v>
@@ -16185,15 +16323,15 @@
       <c r="J272" t="inlineStr"/>
       <c r="K272" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 27 August 2025 11:00am</t>
         </is>
       </c>
       <c r="L272" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45896.45833333334</v>
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N272" s="1" t="n">
@@ -16208,21 +16346,21 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate</t>
+          <t>Future Flight: Regional Demonstrator 2</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2239/overview/7c5a9acd-4b31-414a-8e35-20dd1df3a2a1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2025-07-15 08:20</t>
+          <t>2025-07-09 08:54</t>
         </is>
       </c>
       <c r="E273" s="1" t="n">
-        <v>45853.34722222222</v>
+        <v>45847.37083333333</v>
       </c>
       <c r="F273" t="b">
         <v>1</v>
@@ -16235,15 +16373,15 @@
       <c r="J273" t="inlineStr"/>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Thursday 17 July 2025 11:00am</t>
         </is>
       </c>
       <c r="L273" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45855.45833333334</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N273" s="1" t="n">
@@ -16258,12 +16396,12 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2247/overview/53da287a-c141-48d2-a3eb-f854e14c6578</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -16285,15 +16423,15 @@
       <c r="J274" t="inlineStr"/>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Wednesday 1 October 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L274" s="1" t="n">
-        <v>45931.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N274" s="1" t="n">
@@ -16308,21 +16446,21 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 3</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2245/overview/777781a3-f181-42b3-a05e-86b96754f28d</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025-07-25 08:20</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E275" s="1" t="n">
-        <v>45863.34722222222</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F275" t="b">
         <v>1</v>
@@ -16335,19 +16473,19 @@
       <c r="J275" t="inlineStr"/>
       <c r="K275" t="inlineStr">
         <is>
-          <t>Wednesday 3 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L275" s="1" t="n">
-        <v>45903.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N275" s="1" t="n">
-        <v>45861</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="276">
@@ -16358,21 +16496,21 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Sovereign AI - Proof of concept</t>
+          <t>DRIVE35 Innovation Fund: Collaborate</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2244/overview/84f81488-4936-4551-a315-7ec40cf1065d</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2025-08-07 08:21</t>
+          <t>2025-07-15 08:20</t>
         </is>
       </c>
       <c r="E276" s="1" t="n">
-        <v>45876.34791666667</v>
+        <v>45853.34722222222</v>
       </c>
       <c r="F276" t="b">
         <v>1</v>
@@ -16385,19 +16523,19 @@
       <c r="J276" t="inlineStr"/>
       <c r="K276" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 1 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L276" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45931.45833333334</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>£120,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N276" s="1" t="n">
-        <v>45875</v>
+        <v>45847</v>
       </c>
     </row>
     <row r="277">
@@ -16408,21 +16546,21 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
+          <t>ADOPT Facilitator Support Grant: Round 3</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2251/overview/f40e861a-c7f6-4597-ac5d-2e8d1b4f59f8</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-07-25 08:20</t>
         </is>
       </c>
       <c r="E277" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45863.34722222222</v>
       </c>
       <c r="F277" t="b">
         <v>1</v>
@@ -16435,19 +16573,19 @@
       <c r="J277" t="inlineStr"/>
       <c r="K277" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 3 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L277" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45903.45833333334</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>£8.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N277" s="1" t="n">
-        <v>45882</v>
+        <v>45861</v>
       </c>
     </row>
     <row r="278">
@@ -16458,21 +16596,21 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
+          <t>Sovereign AI - Proof of concept</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2259/overview/9061ddb2-fa12-45c9-8691-d36649c96e9c</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025-08-14 08:20</t>
+          <t>2025-08-07 08:21</t>
         </is>
       </c>
       <c r="E278" s="1" t="n">
-        <v>45883.34722222222</v>
+        <v>45876.34791666667</v>
       </c>
       <c r="F278" t="b">
         <v>1</v>
@@ -16485,19 +16623,19 @@
       <c r="J278" t="inlineStr"/>
       <c r="K278" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L278" s="1" t="n">
-        <v>45980.45833333334</v>
+        <v>45910.45833333334</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>£4.5 million</t>
+          <t>£120,000</t>
         </is>
       </c>
       <c r="N278" s="1" t="n">
-        <v>45882</v>
+        <v>45875</v>
       </c>
     </row>
     <row r="279">
@@ -16508,12 +16646,12 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 3</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2186/overview/e51c18bc-21b3-450d-bdbc-2f43dad3b268</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -16543,7 +16681,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>£3.5 million</t>
+          <t>£8.0 million</t>
         </is>
       </c>
       <c r="N279" s="1" t="n">
@@ -16558,21 +16696,21 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 2</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2185/overview/d5b2aeb3-c2e4-4d78-9be3-f1d9919b0956</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2025-08-26 08:20</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E280" s="1" t="n">
-        <v>45895.34722222222</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F280" t="b">
         <v>1</v>
@@ -16585,19 +16723,19 @@
       <c r="J280" t="inlineStr"/>
       <c r="K280" t="inlineStr">
         <is>
-          <t>Wednesday 10 September 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L280" s="1" t="n">
-        <v>45910.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.5 million</t>
         </is>
       </c>
       <c r="N280" s="1" t="n">
-        <v>45889</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="281">
@@ -16608,21 +16746,21 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 3</t>
+          <t>Obesity Pathway Innovation Programme (OPIP): Strand 1</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2177/overview/696c1e3c-589d-4c37-8958-6255d1dc125a</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2025-08-27 08:18</t>
+          <t>2025-08-14 08:20</t>
         </is>
       </c>
       <c r="E281" s="1" t="n">
-        <v>45896.34583333333</v>
+        <v>45883.34722222222</v>
       </c>
       <c r="F281" t="b">
         <v>1</v>
@@ -16635,19 +16773,19 @@
       <c r="J281" t="inlineStr"/>
       <c r="K281" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L281" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45980.45833333334</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£3.5 million</t>
         </is>
       </c>
       <c r="N281" s="1" t="n">
-        <v>45896</v>
+        <v>45882</v>
       </c>
     </row>
     <row r="282">
@@ -16658,21 +16796,21 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch: EoI – September 2025</t>
+          <t>Analysis for Innovators: National Physical Laboratory Stage 1</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2266/overview/2fcad3ee-b5d6-4f01-8b1a-0e1af3c93023</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2025-09-01 08:20</t>
+          <t>2025-08-26 08:20</t>
         </is>
       </c>
       <c r="E282" s="1" t="n">
-        <v>45901.34722222222</v>
+        <v>45895.34722222222</v>
       </c>
       <c r="F282" t="b">
         <v>1</v>
@@ -16685,15 +16823,19 @@
       <c r="J282" t="inlineStr"/>
       <c r="K282" t="inlineStr">
         <is>
-          <t>Wednesday 17 September 2025 11:00am</t>
+          <t>Wednesday 10 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L282" s="1" t="n">
-        <v>45917.45833333334</v>
-      </c>
-      <c r="M282" t="inlineStr"/>
+        <v>45910.45833333334</v>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>£100,000</t>
+        </is>
+      </c>
       <c r="N282" s="1" t="n">
-        <v>45896</v>
+        <v>45889</v>
       </c>
     </row>
     <row r="283">
@@ -16704,21 +16846,21 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
+          <t>Full ADOPT Grant Round 3</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2265/overview/fae182db-d9e5-4173-bb59-8fde361ccad4</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2025-09-02 08:19</t>
+          <t>2025-08-27 08:18</t>
         </is>
       </c>
       <c r="E283" s="1" t="n">
-        <v>45902.34652777778</v>
+        <v>45896.34583333333</v>
       </c>
       <c r="F283" t="b">
         <v>1</v>
@@ -16731,15 +16873,15 @@
       <c r="J283" t="inlineStr"/>
       <c r="K283" t="inlineStr">
         <is>
-          <t>Wednesday 5 November 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L283" s="1" t="n">
-        <v>45966.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N283" s="1" t="n">
@@ -16754,21 +16896,21 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 4</t>
+          <t>ATI Programme strategic batch: EoI – September 2025</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2273/overview/b30df196-a9a2-4e53-85e1-e3e6aaa5c5b7</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2025-09-04 08:18</t>
+          <t>2025-09-01 08:20</t>
         </is>
       </c>
       <c r="E284" s="1" t="n">
-        <v>45904.34583333333</v>
+        <v>45901.34722222222</v>
       </c>
       <c r="F284" t="b">
         <v>1</v>
@@ -16781,19 +16923,15 @@
       <c r="J284" t="inlineStr"/>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 17 September 2025 11:00am</t>
         </is>
       </c>
       <c r="L284" s="1" t="n">
-        <v>45945.45833333334</v>
-      </c>
-      <c r="M284" t="inlineStr">
-        <is>
-          <t>£2,500</t>
-        </is>
-      </c>
+        <v>45917.45833333334</v>
+      </c>
+      <c r="M284" t="inlineStr"/>
       <c r="N284" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="285">
@@ -16804,21 +16942,21 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 23</t>
+          <t>Farming Innovation Programme: Small R&amp;D Partnership Projects Rd 4</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2010/overview/bcd5cf06-313c-4197-ae47-0035f674717f</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2025-09-05 08:18</t>
+          <t>2025-09-02 08:19</t>
         </is>
       </c>
       <c r="E285" s="1" t="n">
-        <v>45905.34583333333</v>
+        <v>45902.34652777778</v>
       </c>
       <c r="F285" t="b">
         <v>1</v>
@@ -16831,19 +16969,19 @@
       <c r="J285" t="inlineStr"/>
       <c r="K285" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 5 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L285" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45966.45833333334</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N285" s="1" t="n">
-        <v>45903</v>
+        <v>45896</v>
       </c>
     </row>
     <row r="286">
@@ -16854,21 +16992,21 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
+          <t>ADOPT Facilitator Support Grant: Round 4</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2277/overview/7386173a-c074-4617-b7d0-f54f3a458247</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2025-09-12 08:17</t>
+          <t>2025-09-04 08:18</t>
         </is>
       </c>
       <c r="E286" s="1" t="n">
-        <v>45912.34513888889</v>
+        <v>45904.34583333333</v>
       </c>
       <c r="F286" t="b">
         <v>1</v>
@@ -16881,19 +17019,19 @@
       <c r="J286" t="inlineStr"/>
       <c r="K286" t="inlineStr">
         <is>
-          <t>Tuesday 28 October 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L286" s="1" t="n">
-        <v>45958.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N286" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="287">
@@ -16904,21 +17042,21 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
+          <t>Innovate UK Innovation Loans Round 23</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2275/overview/dec9b656-5f30-414e-a169-e11e17d04896</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2025-09-16 08:19</t>
+          <t>2025-09-05 08:18</t>
         </is>
       </c>
       <c r="E287" s="1" t="n">
-        <v>45916.34652777778</v>
+        <v>45905.34583333333</v>
       </c>
       <c r="F287" t="b">
         <v>1</v>
@@ -16931,19 +17069,19 @@
       <c r="J287" t="inlineStr"/>
       <c r="K287" t="inlineStr">
         <is>
-          <t>Wednesday 15 October 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L287" s="1" t="n">
-        <v>45945.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>£40,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N287" s="1" t="n">
-        <v>45910</v>
+        <v>45903</v>
       </c>
     </row>
     <row r="288">
@@ -16954,21 +17092,21 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>UK-Netherlands Co-Innovation and Testbeds Pilot for Quantum Tech</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2288/overview/d547d84e-d652-4ed6-9c85-b12ab8d785d2</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025-09-17 08:18</t>
+          <t>2025-09-12 08:17</t>
         </is>
       </c>
       <c r="E288" s="1" t="n">
-        <v>45917.34583333333</v>
+        <v>45912.34513888889</v>
       </c>
       <c r="F288" t="b">
         <v>1</v>
@@ -16981,17 +17119,19 @@
       <c r="J288" t="inlineStr"/>
       <c r="K288" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr"/>
+          <t>Tuesday 28 October 2025 11:00am</t>
+        </is>
+      </c>
+      <c r="L288" s="1" t="n">
+        <v>45958.45833333334</v>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N288" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="289">
@@ -17002,21 +17142,21 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
+          <t>Contracts for Innovation: Quantum Technologies for Transport - Phase 1</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2292/overview/cdea3182-7495-4cad-8435-f49882f08ec7</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2025-09-18 08:17</t>
+          <t>2025-09-16 08:19</t>
         </is>
       </c>
       <c r="E289" s="1" t="n">
-        <v>45918.34513888889</v>
+        <v>45916.34652777778</v>
       </c>
       <c r="F289" t="b">
         <v>1</v>
@@ -17029,19 +17169,19 @@
       <c r="J289" t="inlineStr"/>
       <c r="K289" t="inlineStr">
         <is>
-          <t>Thursday 4 December 2025 11:00am</t>
+          <t>Wednesday 15 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L289" s="1" t="n">
-        <v>45995.45833333334</v>
+        <v>45945.45833333334</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£40,000</t>
         </is>
       </c>
       <c r="N289" s="1" t="n">
-        <v>45917</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="290">
@@ -17052,21 +17192,21 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Resource efficiency for resilience and sustainability FS</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2025-09-20 08:16</t>
+          <t>2025-09-17 08:18</t>
         </is>
       </c>
       <c r="E290" s="1" t="n">
-        <v>45920.34444444445</v>
+        <v>45917.34583333333</v>
       </c>
       <c r="F290" t="b">
         <v>1</v>
@@ -17079,15 +17219,13 @@
       <c r="J290" t="inlineStr"/>
       <c r="K290" t="inlineStr">
         <is>
-          <t>Monday 3 November 2025 11:00am</t>
-        </is>
-      </c>
-      <c r="L290" s="1" t="n">
-        <v>45964.45833333334</v>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr"/>
       <c r="M290" t="inlineStr">
         <is>
-          <t>£25,000</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N290" s="1" t="n">
@@ -17102,21 +17240,21 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Winter</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2295/overview/cdce9dab-263c-444b-9e91-61f13046bd62</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2025-09-23 08:18</t>
+          <t>2025-09-18 08:17</t>
         </is>
       </c>
       <c r="E291" s="1" t="n">
-        <v>45923.34583333333</v>
+        <v>45918.34513888889</v>
       </c>
       <c r="F291" t="b">
         <v>1</v>
@@ -17129,15 +17267,15 @@
       <c r="J291" t="inlineStr"/>
       <c r="K291" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Thursday 4 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L291" s="1" t="n">
-        <v>45952.45833333334</v>
+        <v>45995.45833333334</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N291" s="1" t="n">
@@ -17152,21 +17290,21 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Farming Innovation Programme: Feasibility Round 4</t>
+          <t>Resource efficiency for resilience and sustainability FS</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2293/overview/2efee934-8622-4686-bc02-a6ac7fc9e5a6</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2025-09-29 08:20</t>
+          <t>2025-09-20 08:16</t>
         </is>
       </c>
       <c r="E292" s="1" t="n">
-        <v>45929.34722222222</v>
+        <v>45920.34444444445</v>
       </c>
       <c r="F292" t="b">
         <v>1</v>
@@ -17179,19 +17317,19 @@
       <c r="J292" t="inlineStr"/>
       <c r="K292" t="inlineStr">
         <is>
-          <t>Wednesday 3 December 2025 11:00am</t>
+          <t>Monday 3 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L292" s="1" t="n">
-        <v>45994.45833333334</v>
+        <v>45964.45833333334</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£25,000</t>
         </is>
       </c>
       <c r="N292" s="1" t="n">
-        <v>45924</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="293">
@@ -17202,21 +17340,21 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Eureka GlobalStars Japan 2026</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C4</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2284/overview/aa6bd2b1-f6e1-4e96-bd4c-0557c10779c8</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2025-10-03 08:17</t>
+          <t>2025-09-23 08:18</t>
         </is>
       </c>
       <c r="E293" s="1" t="n">
-        <v>45933.34513888889</v>
+        <v>45923.34583333333</v>
       </c>
       <c r="F293" t="b">
         <v>1</v>
@@ -17229,19 +17367,19 @@
       <c r="J293" t="inlineStr"/>
       <c r="K293" t="inlineStr">
         <is>
-          <t>Wednesday 21 January 2026 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L293" s="1" t="n">
-        <v>46043.45833333334</v>
+        <v>45952.45833333334</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>£600,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N293" s="1" t="n">
-        <v>45931</v>
+        <v>45917</v>
       </c>
     </row>
     <row r="294">
@@ -17252,21 +17390,21 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Feasibility studies 2</t>
+          <t>Farming Innovation Programme: Feasibility Round 4</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2006/overview/b67973b5-6d46-4a34-a864-bec1212e3fe0</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025-10-10 08:18</t>
+          <t>2025-09-29 08:20</t>
         </is>
       </c>
       <c r="E294" s="1" t="n">
-        <v>45940.34583333333</v>
+        <v>45929.34722222222</v>
       </c>
       <c r="F294" t="b">
         <v>1</v>
@@ -17279,19 +17417,19 @@
       <c r="J294" t="inlineStr"/>
       <c r="K294" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 3 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L294" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>45994.45833333334</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N294" s="1" t="n">
-        <v>45938</v>
+        <v>45924</v>
       </c>
     </row>
     <row r="295">
@@ -17302,21 +17440,21 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – October 2025</t>
+          <t>Eureka GlobalStars Japan 2026</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2276/overview/19635c62-dd91-41d8-a90e-547cdb5acbfa</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025-10-14 08:17</t>
+          <t>2025-10-03 08:17</t>
         </is>
       </c>
       <c r="E295" s="1" t="n">
-        <v>45944.34513888889</v>
+        <v>45933.34513888889</v>
       </c>
       <c r="F295" t="b">
         <v>1</v>
@@ -17329,15 +17467,19 @@
       <c r="J295" t="inlineStr"/>
       <c r="K295" t="inlineStr">
         <is>
-          <t>Wednesday 22 October 2025 11:00am</t>
+          <t>Wednesday 21 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L295" s="1" t="n">
-        <v>45952.45833333334</v>
-      </c>
-      <c r="M295" t="inlineStr"/>
+        <v>46043.45833333334</v>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>£600,000</t>
+        </is>
+      </c>
       <c r="N295" s="1" t="n">
-        <v>45938</v>
+        <v>45931</v>
       </c>
     </row>
     <row r="296">
@@ -17348,21 +17490,21 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Enable</t>
+          <t>CAM Pathfinder: Feasibility studies 2</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2307/overview/8eec43e7-96a5-49d1-97e1-3400321160f9</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-10 08:18</t>
         </is>
       </c>
       <c r="E296" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45940.34583333333</v>
       </c>
       <c r="F296" t="b">
         <v>1</v>
@@ -17375,19 +17517,19 @@
       <c r="J296" t="inlineStr"/>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L296" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N296" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="297">
@@ -17398,21 +17540,21 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>CAM Pathfinder: Demonstrate</t>
+          <t>ATI Programme strategic batch EoI – October 2025</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2317/overview/c946fbde-725e-4f85-bb3f-3219576c4a01</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2025-10-15 08:19</t>
+          <t>2025-10-14 08:17</t>
         </is>
       </c>
       <c r="E297" s="1" t="n">
-        <v>45945.34652777778</v>
+        <v>45944.34513888889</v>
       </c>
       <c r="F297" t="b">
         <v>1</v>
@@ -17425,19 +17567,15 @@
       <c r="J297" t="inlineStr"/>
       <c r="K297" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 22 October 2025 11:00am</t>
         </is>
       </c>
       <c r="L297" s="1" t="n">
-        <v>46008.45833333334</v>
-      </c>
-      <c r="M297" t="inlineStr">
-        <is>
-          <t>£2.0 million</t>
-        </is>
-      </c>
+        <v>45952.45833333334</v>
+      </c>
+      <c r="M297" t="inlineStr"/>
       <c r="N297" s="1" t="n">
-        <v>45945</v>
+        <v>45938</v>
       </c>
     </row>
     <row r="298">
@@ -17448,21 +17586,21 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
+          <t>CAM Pathfinder: Enable</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2318/overview/39cd0e04-6f9c-40da-b0be-8eaae7f1603d</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2025-10-16 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E298" s="1" t="n">
-        <v>45946.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F298" t="b">
         <v>1</v>
@@ -17475,15 +17613,15 @@
       <c r="J298" t="inlineStr"/>
       <c r="K298" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L298" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N298" s="1" t="n">
@@ -17498,21 +17636,21 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 5</t>
+          <t>CAM Pathfinder: Demonstrate</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2315/overview/f02885bb-e043-4a60-8d0c-22242bd77fa9</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2025-10-17 08:19</t>
+          <t>2025-10-15 08:19</t>
         </is>
       </c>
       <c r="E299" s="1" t="n">
-        <v>45947.34652777778</v>
+        <v>45945.34652777778</v>
       </c>
       <c r="F299" t="b">
         <v>1</v>
@@ -17525,15 +17663,15 @@
       <c r="J299" t="inlineStr"/>
       <c r="K299" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L299" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N299" s="1" t="n">
@@ -17548,21 +17686,21 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Battery Innovation Feasibility Studies Round 1</t>
+          <t>Launchpad: life and health sciences, Northern Ireland – Rd3 MFA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2305/overview/fe565f48-36a8-4d8b-8515-e89d750f259c</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-16 08:19</t>
         </is>
       </c>
       <c r="E300" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45946.34652777778</v>
       </c>
       <c r="F300" t="b">
         <v>1</v>
@@ -17575,15 +17713,15 @@
       <c r="J300" t="inlineStr"/>
       <c r="K300" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L300" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N300" s="1" t="n">
@@ -17598,21 +17736,21 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Battery Innovation Concept Development Round 1</t>
+          <t>ADOPT Facilitator Support Grant: Round 5</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2299/overview/0a26e49f-fa03-4096-aa8b-3eb39b68f20d</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2025-10-18 08:16</t>
+          <t>2025-10-17 08:19</t>
         </is>
       </c>
       <c r="E301" s="1" t="n">
-        <v>45948.34444444445</v>
+        <v>45947.34652777778</v>
       </c>
       <c r="F301" t="b">
         <v>1</v>
@@ -17625,15 +17763,15 @@
       <c r="J301" t="inlineStr"/>
       <c r="K301" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L301" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N301" s="1" t="n">
@@ -17648,21 +17786,21 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>The Agentic AI Pioneers Prize</t>
+          <t>Battery Innovation Feasibility Studies Round 1</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2313/overview/508ab35f-0e07-4e84-8e31-bbbcb619bc9e</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2025-10-21 08:20</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E302" s="1" t="n">
-        <v>45951.34722222222</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F302" t="b">
         <v>1</v>
@@ -17675,13 +17813,17 @@
       <c r="J302" t="inlineStr"/>
       <c r="K302" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L302" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M302" t="inlineStr"/>
+        <v>46008.45833333334</v>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N302" s="1" t="n">
         <v>45945</v>
       </c>
@@ -17694,21 +17836,21 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy efficiency – industrial research</t>
+          <t>Battery Innovation Concept Development Round 1</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2314/overview/4d1e65d7-b380-41b7-8dcf-b25cd26b9ab5</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-18 08:16</t>
         </is>
       </c>
       <c r="E303" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45948.34444444445</v>
       </c>
       <c r="F303" t="b">
         <v>1</v>
@@ -17721,19 +17863,19 @@
       <c r="J303" t="inlineStr"/>
       <c r="K303" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L303" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N303" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="304">
@@ -17744,21 +17886,21 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
+          <t>The Agentic AI Pioneers Prize</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2316/overview/fa0eeab0-3021-4cbc-8975-5bd45a7d642a</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2025-10-22 08:21</t>
+          <t>2025-10-21 08:20</t>
         </is>
       </c>
       <c r="E304" s="1" t="n">
-        <v>45952.34791666667</v>
+        <v>45951.34722222222</v>
       </c>
       <c r="F304" t="b">
         <v>1</v>
@@ -17771,19 +17913,15 @@
       <c r="J304" t="inlineStr"/>
       <c r="K304" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L304" s="1" t="n">
-        <v>46001.45833333334</v>
-      </c>
-      <c r="M304" t="inlineStr">
-        <is>
-          <t>£150,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M304" t="inlineStr"/>
       <c r="N304" s="1" t="n">
-        <v>45952</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="305">
@@ -17794,21 +17932,21 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant Round 4</t>
+          <t>MSI: SME resource and energy efficiency – industrial research</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2328/overview/79cb058a-71b3-459a-93c2-8c96ecf7f18a</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2025-10-23 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E305" s="1" t="n">
-        <v>45953.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F305" t="b">
         <v>1</v>
@@ -17829,7 +17967,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N305" s="1" t="n">
@@ -17844,21 +17982,21 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 24</t>
+          <t>MSI: SME resource and energy   efficiency – feasibility studies</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2327/overview/bd7d1a37-69dc-4d09-8615-2bae4bcf3666</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2025-10-24 08:19</t>
+          <t>2025-10-22 08:21</t>
         </is>
       </c>
       <c r="E306" s="1" t="n">
-        <v>45954.34652777778</v>
+        <v>45952.34791666667</v>
       </c>
       <c r="F306" t="b">
         <v>1</v>
@@ -17871,15 +18009,15 @@
       <c r="J306" t="inlineStr"/>
       <c r="K306" t="inlineStr">
         <is>
-          <t>Wednesday 7 January 2026 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L306" s="1" t="n">
-        <v>46029.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N306" s="1" t="n">
@@ -17894,21 +18032,21 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
+          <t>Full ADOPT Grant Round 4</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2298/overview/71fd7055-502d-4f85-9127-749156a80fe6</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2025-10-25 08:16</t>
+          <t>2025-10-23 08:19</t>
         </is>
       </c>
       <c r="E307" s="1" t="n">
-        <v>45955.34444444445</v>
+        <v>45953.34652777778</v>
       </c>
       <c r="F307" t="b">
         <v>1</v>
@@ -17921,15 +18059,15 @@
       <c r="J307" t="inlineStr"/>
       <c r="K307" t="inlineStr">
         <is>
-          <t>Wednesday 26 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L307" s="1" t="n">
-        <v>45987.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N307" s="1" t="n">
@@ -17944,21 +18082,21 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>National Materials Innovation Programme: Feasibility Studies</t>
+          <t>Innovate UK Innovation Loans Round 24</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2322/overview/1b933876-5f58-4dec-85ab-68b8c2722211</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2025-10-31 08:18</t>
+          <t>2025-10-24 08:19</t>
         </is>
       </c>
       <c r="E308" s="1" t="n">
-        <v>45961.34583333333</v>
+        <v>45954.34652777778</v>
       </c>
       <c r="F308" t="b">
         <v>1</v>
@@ -17971,19 +18109,19 @@
       <c r="J308" t="inlineStr"/>
       <c r="K308" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 7 January 2026 11:00am</t>
         </is>
       </c>
       <c r="L308" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46029.45833333334</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N308" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="309">
@@ -17994,21 +18132,21 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 4</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2290/overview/8dd45f5c-3f38-4e38-b733-42b6cf601292</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-25 08:16</t>
         </is>
       </c>
       <c r="E309" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45955.34444444445</v>
       </c>
       <c r="F309" t="b">
         <v>1</v>
@@ -18029,11 +18167,11 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>£3.4 million</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N309" s="1" t="n">
-        <v>45959</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="310">
@@ -18044,21 +18182,21 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Increasing EV charging capacity on the strategic road network</t>
+          <t>National Materials Innovation Programme: Feasibility Studies</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2326/overview/ca8aab61-a03b-431f-94a8-5c9b008495d5</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2025-11-04 08:20</t>
+          <t>2025-10-31 08:18</t>
         </is>
       </c>
       <c r="E310" s="1" t="n">
-        <v>45965.34722222222</v>
+        <v>45961.34583333333</v>
       </c>
       <c r="F310" t="b">
         <v>1</v>
@@ -18071,15 +18209,15 @@
       <c r="J310" t="inlineStr"/>
       <c r="K310" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L310" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N310" s="1" t="n">
@@ -18094,21 +18232,21 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
+          <t>UK-Canada Quantum Communications and Networking Demonstrator</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2335/overview/64e26f1b-8564-4539-b3ca-1b15ebf4f94a</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E311" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F311" t="b">
         <v>1</v>
@@ -18121,19 +18259,19 @@
       <c r="J311" t="inlineStr"/>
       <c r="K311" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 26 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L311" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>45987.45833333334</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£3.4 million</t>
         </is>
       </c>
       <c r="N311" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="312">
@@ -18144,21 +18282,21 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
+          <t>Increasing EV charging capacity on the strategic road network</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2304/overview/9ea6670e-83fd-43f9-972f-e0eff8fe77a8</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2025-11-05 08:19</t>
+          <t>2025-11-04 08:20</t>
         </is>
       </c>
       <c r="E312" s="1" t="n">
-        <v>45966.34652777778</v>
+        <v>45965.34722222222</v>
       </c>
       <c r="F312" t="b">
         <v>1</v>
@@ -18171,19 +18309,19 @@
       <c r="J312" t="inlineStr"/>
       <c r="K312" t="inlineStr">
         <is>
-          <t>Wednesday 10 December 2025 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L312" s="1" t="n">
-        <v>46001.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N312" s="1" t="n">
-        <v>45966</v>
+        <v>45959</v>
       </c>
     </row>
     <row r="313">
@@ -18194,12 +18332,12 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>ATI Programme strategic batch EoI – November 2025</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D small projects</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2333/overview/f5431c75-e2e1-48f4-bc8e-62d52121cb6f</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -18221,13 +18359,17 @@
       <c r="J313" t="inlineStr"/>
       <c r="K313" t="inlineStr">
         <is>
-          <t>Wednesday 19 November 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L313" s="1" t="n">
-        <v>45980.45833333334</v>
-      </c>
-      <c r="M313" t="inlineStr"/>
+        <v>46001.45833333334</v>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>£1.0 million</t>
+        </is>
+      </c>
       <c r="N313" s="1" t="n">
         <v>45966</v>
       </c>
@@ -18240,21 +18382,21 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
+          <t>Biomedical Catalyst 2025: Industry led R&amp;D large projects</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2332/overview/bf6bd8c3-e550-478d-b374-a3cb0fb4d3d3</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2025-11-11 08:19</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E314" s="1" t="n">
-        <v>45972.34652777778</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F314" t="b">
         <v>1</v>
@@ -18267,15 +18409,15 @@
       <c r="J314" t="inlineStr"/>
       <c r="K314" t="inlineStr">
         <is>
-          <t>Wednesday 17 December 2025 11:00am</t>
+          <t>Wednesday 10 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L314" s="1" t="n">
-        <v>46008.45833333334</v>
+        <v>46001.45833333334</v>
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N314" s="1" t="n">
@@ -18290,21 +18432,21 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Women in Innovation Awards 2025/26</t>
+          <t>ATI Programme strategic batch EoI – November 2025</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2334/overview/4af06b80-2953-4cb3-8cc0-987ec5a2f322</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2025-11-27 13:23</t>
+          <t>2025-11-05 08:19</t>
         </is>
       </c>
       <c r="E315" s="1" t="n">
-        <v>45988.55763888889</v>
+        <v>45966.34652777778</v>
       </c>
       <c r="F315" t="b">
         <v>1</v>
@@ -18317,19 +18459,15 @@
       <c r="J315" t="inlineStr"/>
       <c r="K315" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 19 November 2025 11:00am</t>
         </is>
       </c>
       <c r="L315" s="1" t="n">
-        <v>46057.45833333334</v>
-      </c>
-      <c r="M315" t="inlineStr">
-        <is>
-          <t>£75,000</t>
-        </is>
-      </c>
+        <v>45980.45833333334</v>
+      </c>
+      <c r="M315" t="inlineStr"/>
       <c r="N315" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="316">
@@ -18340,21 +18478,21 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
+          <t>DRIVE35 Scale-up: Feasibility Studies 2</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2341/overview/4b0efce9-75b8-4e84-97c0-fc6277396586</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2025-12-02 08:22</t>
+          <t>2025-11-11 08:19</t>
         </is>
       </c>
       <c r="E316" s="1" t="n">
-        <v>45993.34861111111</v>
+        <v>45972.34652777778</v>
       </c>
       <c r="F316" t="b">
         <v>1</v>
@@ -18367,19 +18505,19 @@
       <c r="J316" t="inlineStr"/>
       <c r="K316" t="inlineStr">
         <is>
-          <t>Wednesday 4 February 2026 11:00am</t>
+          <t>Wednesday 17 December 2025 11:00am</t>
         </is>
       </c>
       <c r="L316" s="1" t="n">
-        <v>46057.45833333334</v>
+        <v>46008.45833333334</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N316" s="1" t="n">
-        <v>45987</v>
+        <v>45966</v>
       </c>
     </row>
     <row r="317">
@@ -18390,21 +18528,21 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
+          <t>Women in Innovation Awards 2025/26</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2337/overview/3750b1cd-2080-4a1c-82c0-003fbaafdd2d</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2025-12-11 08:22</t>
+          <t>2025-11-27 13:23</t>
         </is>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46002.34861111111</v>
+        <v>45988.55763888889</v>
       </c>
       <c r="F317" t="b">
         <v>1</v>
@@ -18417,19 +18555,19 @@
       <c r="J317" t="inlineStr"/>
       <c r="K317" t="inlineStr">
         <is>
-          <t>Tuesday 3 February 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L317" s="1" t="n">
-        <v>46056.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£75,000</t>
         </is>
       </c>
       <c r="N317" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="318">
@@ -18440,21 +18578,21 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 5</t>
+          <t>Knowledge Transfer Partnership (KTP): 2025 – 2026 Round 5</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2354/overview/c7008321-f651-45c5-a409-c3215231fbb4</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2025-12-12 08:22</t>
+          <t>2025-12-02 08:22</t>
         </is>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46003.34861111111</v>
+        <v>45993.34861111111</v>
       </c>
       <c r="F318" t="b">
         <v>1</v>
@@ -18475,11 +18613,11 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£8,500</t>
         </is>
       </c>
       <c r="N318" s="1" t="n">
-        <v>46001</v>
+        <v>45987</v>
       </c>
     </row>
     <row r="319">
@@ -18490,21 +18628,21 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 6</t>
+          <t>Innovate UK Growth Catalyst – Investor Partnerships Round 2</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2360/overview/37d8f6e1-5600-4e9e-bbfc-11bc320f8808</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-11 08:22</t>
         </is>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46002.34861111111</v>
       </c>
       <c r="F319" t="b">
         <v>1</v>
@@ -18517,19 +18655,19 @@
       <c r="J319" t="inlineStr"/>
       <c r="K319" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Tuesday 3 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L319" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46056.45833333334</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N319" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="320">
@@ -18540,21 +18678,21 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
+          <t>Full ADOPT Grant: Round 5</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2358/overview/f93f32c2-dd04-474d-bc35-a8af1ecac1a9</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2025-12-18 08:21</t>
+          <t>2025-12-12 08:22</t>
         </is>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46009.34791666667</v>
+        <v>46003.34861111111</v>
       </c>
       <c r="F320" t="b">
         <v>1</v>
@@ -18567,19 +18705,19 @@
       <c r="J320" t="inlineStr"/>
       <c r="K320" t="inlineStr">
         <is>
-          <t>Thursday 7 May 2026 11:00am</t>
+          <t>Wednesday 4 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L320" s="1" t="n">
-        <v>46149.45833333334</v>
+        <v>46057.45833333334</v>
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N320" s="1" t="n">
-        <v>46008</v>
+        <v>46001</v>
       </c>
     </row>
     <row r="321">
@@ -18590,21 +18728,21 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – mid stage</t>
+          <t>ADOPT Facilitator Support Grant: Round 6</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2371/overview/471bfe91-9f9c-4086-a28a-15296f1957e2</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F321" t="b">
         <v>1</v>
@@ -18617,19 +18755,19 @@
       <c r="J321" t="inlineStr"/>
       <c r="K321" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L321" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N321" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="322">
@@ -18640,21 +18778,21 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – late stage</t>
+          <t>Commercialising Knowledge Assets Fund (CKAF) Spring</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2369/overview/abf7d399-81b9-4f33-b592-51825a288c37</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-01-06 08:22</t>
+          <t>2025-12-18 08:21</t>
         </is>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46028.34861111111</v>
+        <v>46009.34791666667</v>
       </c>
       <c r="F322" t="b">
         <v>1</v>
@@ -18667,19 +18805,19 @@
       <c r="J322" t="inlineStr"/>
       <c r="K322" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Thursday 7 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L322" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46149.45833333334</v>
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N322" s="1" t="n">
-        <v>46022</v>
+        <v>46008</v>
       </c>
     </row>
     <row r="323">
@@ -18690,12 +18828,12 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Energy catalyst round 11 – early stage</t>
+          <t>Energy catalyst round 11 – mid stage</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2363/overview/9f759af1-3732-4d15-995d-053e28025d22</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -18725,7 +18863,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N323" s="1" t="n">
@@ -18740,12 +18878,12 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
+          <t>Energy catalyst round 11 – late stage</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2364/overview/b9d4dedf-d22a-41d1-9ca2-6c5a279519be</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -18767,15 +18905,15 @@
       <c r="J324" t="inlineStr"/>
       <c r="K324" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L324" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N324" s="1" t="n">
@@ -18790,12 +18928,12 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
+          <t>Energy catalyst round 11 – early stage</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2362/overview/640b2f4e-8571-4aef-9e2a-67e35db3db77</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -18817,15 +18955,15 @@
       <c r="J325" t="inlineStr"/>
       <c r="K325" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L325" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46106.45833333334</v>
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>£25.0 million</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N325" s="1" t="n">
@@ -18840,21 +18978,21 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Innovate UK Innovation Loans Round 25</t>
+          <t>DRIVE35 Innovation Fund: Demonstrate 2</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2351/overview/349c38f5-5ed2-4cf4-a324-bda2d6cd1e67</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-01-08 08:22</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46030.34861111111</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F326" t="b">
         <v>1</v>
@@ -18867,19 +19005,19 @@
       <c r="J326" t="inlineStr"/>
       <c r="K326" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L326" s="1" t="n">
-        <v>46085.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N326" s="1" t="n">
-        <v>46029</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="327">
@@ -18890,21 +19028,21 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
+          <t>DRIVE35 Innovation Fund: Collaborate 2</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2350/overview/dbd41be3-14ea-4c83-8774-eb28a8703d57</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-01-15 08:23</t>
+          <t>2026-01-06 08:22</t>
         </is>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46037.34930555556</v>
+        <v>46028.34861111111</v>
       </c>
       <c r="F327" t="b">
         <v>1</v>
@@ -18917,19 +19055,19 @@
       <c r="J327" t="inlineStr"/>
       <c r="K327" t="inlineStr">
         <is>
-          <t>Wednesday 11 February 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L327" s="1" t="n">
-        <v>46064.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>£32,000</t>
+          <t>£25.0 million</t>
         </is>
       </c>
       <c r="N327" s="1" t="n">
-        <v>46036</v>
+        <v>46022</v>
       </c>
     </row>
     <row r="328">
@@ -18940,21 +19078,21 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
+          <t>Innovate UK Innovation Loans Round 25</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2373/overview/609dc5dd-d3e8-4f51-af3a-3eb1b3314710</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-01-20 08:24</t>
+          <t>2026-01-08 08:22</t>
         </is>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46042.35</v>
+        <v>46030.34861111111</v>
       </c>
       <c r="F328" t="b">
         <v>1</v>
@@ -18967,19 +19105,19 @@
       <c r="J328" t="inlineStr"/>
       <c r="K328" t="inlineStr">
         <is>
-          <t>Wednesday 25 February 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L328" s="1" t="n">
-        <v>46078.45833333334</v>
+        <v>46085.45833333334</v>
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>£150,000</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N328" s="1" t="n">
-        <v>46036</v>
+        <v>46029</v>
       </c>
     </row>
     <row r="329">
@@ -18990,21 +19128,21 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation FS</t>
+          <t>Cyber Security Academic Startup Accelerator Programme Y10 Phase 1</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2376/overview/1b9b9265-ca4b-4f8c-a0c2-577cb8713642</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-01-26 12:10</t>
+          <t>2026-01-15 08:23</t>
         </is>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46048.50694444445</v>
+        <v>46037.34930555556</v>
       </c>
       <c r="F329" t="b">
         <v>1</v>
@@ -19017,19 +19155,19 @@
       <c r="J329" t="inlineStr"/>
       <c r="K329" t="inlineStr">
         <is>
-          <t>Wednesday 11 March 2026 11:00am</t>
+          <t>Wednesday 11 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L329" s="1" t="n">
-        <v>46092.45833333334</v>
+        <v>46064.45833333334</v>
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£32,000</t>
         </is>
       </c>
       <c r="N329" s="1" t="n">
-        <v>46043</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="330">
@@ -19040,21 +19178,21 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
+          <t>Ofgem Strategic Innovation Fund Round 5 Discovery C5</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2346/overview/e172ee7c-3050-4d47-bf11-235cfe76c1e1</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-20 08:24</t>
         </is>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46042.35</v>
       </c>
       <c r="F330" t="b">
         <v>1</v>
@@ -19067,19 +19205,19 @@
       <c r="J330" t="inlineStr"/>
       <c r="K330" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 25 February 2026 11:00am</t>
         </is>
       </c>
       <c r="L330" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46078.45833333334</v>
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>£225,000</t>
+          <t>£150,000</t>
         </is>
       </c>
       <c r="N330" s="1" t="n">
-        <v>46050</v>
+        <v>46036</v>
       </c>
     </row>
     <row r="331">
@@ -19090,21 +19228,21 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
+          <t>Advanced manufacturing supply chain innovation FS</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2384/overview/2ad8ce21-d3f6-48bf-b55a-5af2a892a1e0</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-01-28 10:24</t>
+          <t>2026-01-26 12:10</t>
         </is>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46050.43333333333</v>
+        <v>46048.50694444445</v>
       </c>
       <c r="F331" t="b">
         <v>1</v>
@@ -19117,19 +19255,19 @@
       <c r="J331" t="inlineStr"/>
       <c r="K331" t="inlineStr">
         <is>
-          <t>Wednesday 18 March 2026 11:00am</t>
+          <t>Wednesday 11 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L331" s="1" t="n">
-        <v>46099.45833333334</v>
+        <v>46092.45833333334</v>
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N331" s="1" t="n">
-        <v>46050</v>
+        <v>46043</v>
       </c>
     </row>
     <row r="332">
@@ -19140,21 +19278,21 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Robotics Adoption Programme skills development</t>
+          <t>TechLocal: Connecting Local Talent to Local Tech Jobs</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2378/overview/ae120ce2-7b72-4cf2-8dde-f78b02d5996d</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-02-02 10:39</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46055.44375</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F332" t="b">
         <v>1</v>
@@ -19167,15 +19305,15 @@
       <c r="J332" t="inlineStr"/>
       <c r="K332" t="inlineStr">
         <is>
-          <t>Wednesday 25 March 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L332" s="1" t="n">
-        <v>46106.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£225,000</t>
         </is>
       </c>
       <c r="N332" s="1" t="n">
@@ -19190,21 +19328,21 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
+          <t>TechLocal AI Professional Degree and Traineeship Accelerator</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2375/overview/6431359e-eb5c-4f76-b49d-299948107fbd</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-01-28 10:24</t>
         </is>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46050.43333333333</v>
       </c>
       <c r="F333" t="b">
         <v>1</v>
@@ -19217,15 +19355,15 @@
       <c r="J333" t="inlineStr"/>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 18 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L333" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46099.45833333334</v>
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£300,000</t>
         </is>
       </c>
       <c r="N333" s="1" t="n">
@@ -19240,21 +19378,21 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
+          <t>Robotics Adoption Programme skills development</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2387/overview/daca31c2-8395-4bc2-a5da-55eb1e432fa4</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-02-03 10:35</t>
+          <t>2026-02-02 10:39</t>
         </is>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46056.44097222222</v>
+        <v>46055.44375</v>
       </c>
       <c r="F334" t="b">
         <v>1</v>
@@ -19267,13 +19405,17 @@
       <c r="J334" t="inlineStr"/>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 25 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L334" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M334" t="inlineStr"/>
+        <v>46106.45833333334</v>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>£500,000</t>
+        </is>
+      </c>
       <c r="N334" s="1" t="n">
         <v>46050</v>
       </c>
@@ -19286,12 +19428,12 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 1</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2380/overview/3e170dd3-4458-4c7e-a096-e0ea50b88040</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -19313,13 +19455,17 @@
       <c r="J335" t="inlineStr"/>
       <c r="K335" t="inlineStr">
         <is>
-          <t>Wednesday 4 March 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L335" s="1" t="n">
-        <v>46085.45833333334</v>
-      </c>
-      <c r="M335" t="inlineStr"/>
+        <v>46113.45833333334</v>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N335" s="1" t="n">
         <v>46050</v>
       </c>
@@ -19332,21 +19478,21 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 6</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: late stage</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2389/overview/a7f7d874-8b6b-45d6-b1e1-1e88e11a1ea5</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-02-09 10:53</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46062.45347222222</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F336" t="b">
         <v>1</v>
@@ -19359,19 +19505,15 @@
       <c r="J336" t="inlineStr"/>
       <c r="K336" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L336" s="1" t="n">
-        <v>46120.45833333334</v>
-      </c>
-      <c r="M336" t="inlineStr">
-        <is>
-          <t>£100,000</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M336" t="inlineStr"/>
       <c r="N336" s="1" t="n">
-        <v>46057</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="337">
@@ -19382,21 +19524,21 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Zero Emission Flight Demonstrator Round 1</t>
+          <t>Biomedical Catalyst Accelerator Provider Pool EoI: early stage</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2388/overview/08b8ab63-085d-4d79-ae83-e8c1698cb327</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-03 10:35</t>
         </is>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46056.44097222222</v>
       </c>
       <c r="F337" t="b">
         <v>1</v>
@@ -19409,19 +19551,15 @@
       <c r="J337" t="inlineStr"/>
       <c r="K337" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 4 March 2026 11:00am</t>
         </is>
       </c>
       <c r="L337" s="1" t="n">
-        <v>46113.45833333334</v>
-      </c>
-      <c r="M337" t="inlineStr">
-        <is>
-          <t>£5.0 million</t>
-        </is>
-      </c>
+        <v>46085.45833333334</v>
+      </c>
+      <c r="M337" t="inlineStr"/>
       <c r="N337" s="1" t="n">
-        <v>46064</v>
+        <v>46050</v>
       </c>
     </row>
     <row r="338">
@@ -19432,21 +19570,21 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
+          <t>Full ADOPT Grant: Round 6</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2385/overview/2343c344-807d-41a1-9551-05ac5420ba11</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-02-12 10:40</t>
+          <t>2026-02-09 10:53</t>
         </is>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46065.44444444445</v>
+        <v>46062.45347222222</v>
       </c>
       <c r="F338" t="b">
         <v>1</v>
@@ -19459,19 +19597,19 @@
       <c r="J338" t="inlineStr"/>
       <c r="K338" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L338" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N338" s="1" t="n">
-        <v>46064</v>
+        <v>46057</v>
       </c>
     </row>
     <row r="339">
@@ -19482,12 +19620,12 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
+          <t>Zero Emission Flight Demonstrator Round 1</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2397/overview/752074ec-5f01-46d8-863f-596300a11651</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -19509,15 +19647,15 @@
       <c r="J339" t="inlineStr"/>
       <c r="K339" t="inlineStr">
         <is>
-          <t>Wednesday 6 May 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L339" s="1" t="n">
-        <v>46148.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>£10.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N339" s="1" t="n">
@@ -19532,21 +19670,21 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
+          <t>Contracts for Innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2395/overview/3d49fbc4-6e09-4dd8-9ac8-8e5f88facd8d</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-02-13 10:35</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46066.44097222222</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F340" t="b">
         <v>1</v>
@@ -19559,15 +19697,15 @@
       <c r="J340" t="inlineStr"/>
       <c r="K340" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L340" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N340" s="1" t="n">
@@ -19582,21 +19720,21 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: industrial human relevant drug models</t>
+          <t>Advancing innovation in drug and alcohol addiction healthcare</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2394/overview/33b56af8-353f-46ac-bb66-a0928731c0fc</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-02-17 10:40</t>
+          <t>2026-02-12 10:40</t>
         </is>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46070.44444444445</v>
+        <v>46065.44444444445</v>
       </c>
       <c r="F341" t="b">
         <v>1</v>
@@ -19609,15 +19747,15 @@
       <c r="J341" t="inlineStr"/>
       <c r="K341" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 6 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L341" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46148.45833333334</v>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>£200,000</t>
+          <t>£10.0 million</t>
         </is>
       </c>
       <c r="N341" s="1" t="n">
@@ -19632,21 +19770,21 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms</t>
+          <t>UK-Germany Collaborative Innovation for Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2392/overview/b8b93732-6326-4aed-9af3-334e4cc5ecc0</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-02-20 10:32</t>
+          <t>2026-02-13 10:35</t>
         </is>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46073.43888888889</v>
+        <v>46066.44097222222</v>
       </c>
       <c r="F342" t="b">
         <v>1</v>
@@ -19659,19 +19797,19 @@
       <c r="J342" t="inlineStr"/>
       <c r="K342" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L342" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N342" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="343">
@@ -19682,21 +19820,21 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Robotics Adoption Hubs</t>
+          <t>Contracts for Innovation: industrial human relevant drug models</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2396/overview/d55398bb-ff62-43b9-9ee1-bf3fa4b95c5c</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-17 10:40</t>
         </is>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46070.44444444445</v>
       </c>
       <c r="F343" t="b">
         <v>1</v>
@@ -19717,11 +19855,11 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>£7.5 million</t>
+          <t>£200,000</t>
         </is>
       </c>
       <c r="N343" s="1" t="n">
-        <v>46071</v>
+        <v>46064</v>
       </c>
     </row>
     <row r="344">
@@ -19732,21 +19870,21 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Robotics Adoption Central Convening Body</t>
+          <t>Semiconductors and components for smart electronic platforms</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2403/overview/4b54c133-c9b2-4572-9cca-2a7a4f69e5b8</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-02-24 10:43</t>
+          <t>2026-02-20 10:32</t>
         </is>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46077.44652777778</v>
+        <v>46073.43888888889</v>
       </c>
       <c r="F344" t="b">
         <v>1</v>
@@ -19759,11 +19897,11 @@
       <c r="J344" t="inlineStr"/>
       <c r="K344" t="inlineStr">
         <is>
-          <t>Wednesday 15 April 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L344" s="1" t="n">
-        <v>46127.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M344" t="inlineStr">
         <is>
@@ -19782,21 +19920,21 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 7</t>
+          <t>Robotics Adoption Hubs</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2408/overview/ad7d7d36-af60-48be-91b0-f3208cf7c1d4</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-02-26 10:40</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46079.44444444445</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F345" t="b">
         <v>1</v>
@@ -19809,19 +19947,19 @@
       <c r="J345" t="inlineStr"/>
       <c r="K345" t="inlineStr">
         <is>
-          <t>Wednesday 8 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L345" s="1" t="n">
-        <v>46120.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£7.5 million</t>
         </is>
       </c>
       <c r="N345" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="346">
@@ -19832,21 +19970,21 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
+          <t>Robotics Adoption Central Convening Body</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2409/overview/c7e5dd6a-9f34-4614-b548-214b76190c14</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-03-03 10:34</t>
+          <t>2026-02-24 10:43</t>
         </is>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46084.44027777778</v>
+        <v>46077.44652777778</v>
       </c>
       <c r="F346" t="b">
         <v>1</v>
@@ -19859,19 +19997,19 @@
       <c r="J346" t="inlineStr"/>
       <c r="K346" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 15 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L346" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46127.45833333334</v>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N346" s="1" t="n">
-        <v>46078</v>
+        <v>46071</v>
       </c>
     </row>
     <row r="347">
@@ -19882,21 +20020,21 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
+          <t>ADOPT Facilitator Support Grant: Round 7</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2404/overview/99693fa4-0f17-4de8-b812-34f2be37a4d0</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-02-26 10:40</t>
         </is>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46079.44444444445</v>
       </c>
       <c r="F347" t="b">
         <v>1</v>
@@ -19909,19 +20047,19 @@
       <c r="J347" t="inlineStr"/>
       <c r="K347" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 8 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L347" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46120.45833333334</v>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>£6.0 million</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N347" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="348">
@@ -19932,21 +20070,21 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
+          <t>SNPN 5G Assured Integration (CR&amp;D)</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2400/overview/cbbc48e2-d78e-42cd-b570-330f702ba82f</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-03-11 10:34</t>
+          <t>2026-03-03 10:34</t>
         </is>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46092.44027777778</v>
+        <v>46084.44027777778</v>
       </c>
       <c r="F348" t="b">
         <v>1</v>
@@ -19959,19 +20097,19 @@
       <c r="J348" t="inlineStr"/>
       <c r="K348" t="inlineStr">
         <is>
-          <t>Wednesday 15 July 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L348" s="1" t="n">
-        <v>46218.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N348" s="1" t="n">
-        <v>46092</v>
+        <v>46078</v>
       </c>
     </row>
     <row r="349">
@@ -19982,12 +20120,12 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
+          <t>Clean Maritime Demonstration Competition 7: Pre-deployment trials</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2415/overview/fa34afe8-b2e7-4cda-b77b-cf952d26a27a</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -20017,7 +20155,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>£15.0 million</t>
+          <t>£6.0 million</t>
         </is>
       </c>
       <c r="N349" s="1" t="n">
@@ -20032,21 +20170,21 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>AI Champions: Frontier AI Phase 1</t>
+          <t>Clean Maritime Demonstration Competition 7: Feasibility studies</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2416/overview/f49610a2-5e82-4898-b357-10f80154a2b8</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-03-12 10:34</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46093.44027777778</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F350" t="b">
         <v>1</v>
@@ -20059,15 +20197,15 @@
       <c r="J350" t="inlineStr"/>
       <c r="K350" t="inlineStr">
         <is>
-          <t>Wednesday 29 April 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L350" s="1" t="n">
-        <v>46141.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N350" s="1" t="n">
@@ -20082,21 +20220,21 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Frontier AI Discovery</t>
+          <t>Clean Maritime Demonstration Competition 7: Deployment trials</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2414/overview/3409b968-a2b7-44e7-83a7-c2d3e8ad8f8e</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-11 10:34</t>
         </is>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46092.44027777778</v>
       </c>
       <c r="F351" t="b">
         <v>1</v>
@@ -20109,15 +20247,15 @@
       <c r="J351" t="inlineStr"/>
       <c r="K351" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 15 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L351" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46218.45833333334</v>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£15.0 million</t>
         </is>
       </c>
       <c r="N351" s="1" t="n">
@@ -20132,21 +20270,21 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Secure Software for Resilient Growth</t>
+          <t>AI Champions: Frontier AI Phase 1</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2419/overview/bb8d7d28-0e63-4ee1-bf4a-790dfb3ae02f</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-03-17 10:45</t>
+          <t>2026-03-12 10:34</t>
         </is>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46098.44791666666</v>
+        <v>46093.44027777778</v>
       </c>
       <c r="F352" t="b">
         <v>1</v>
@@ -20167,7 +20305,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>£750,000</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N352" s="1" t="n">
@@ -20182,12 +20320,12 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
+          <t>Frontier AI Discovery</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2422/overview/a5c16dd4-c60d-4cc1-8035-33fe76a52489</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -20209,15 +20347,15 @@
       <c r="J353" t="inlineStr"/>
       <c r="K353" t="inlineStr">
         <is>
-          <t>Wednesday 22 April 2026 11:00am</t>
+          <t>Wednesday 10 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L353" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46183.45833333334</v>
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N353" s="1" t="n">
@@ -20232,21 +20370,21 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Frontier AI Benchmarking Datasets</t>
+          <t>Secure Software for Resilient Growth</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2421/overview/3d6991fa-73b2-48c0-93eb-cc5393b5cf3d</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-03-23 10:49</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46104.45069444444</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F354" t="b">
         <v>1</v>
@@ -20259,11 +20397,11 @@
       <c r="J354" t="inlineStr"/>
       <c r="K354" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 29 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L354" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46141.45833333334</v>
       </c>
       <c r="M354" t="inlineStr">
         <is>
@@ -20271,7 +20409,7 @@
         </is>
       </c>
       <c r="N354" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="355">
@@ -20282,21 +20420,21 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Medicines Manufacturing: Labs of the Future</t>
+          <t>Advanced Manufacturing Supply Chains: Potential High Growth SMEs</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2423/overview/6207ec15-42c0-424f-a3b7-6bd3bfa11ff1</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-17 10:45</t>
         </is>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46098.44791666666</v>
       </c>
       <c r="F355" t="b">
         <v>1</v>
@@ -20309,19 +20447,19 @@
       <c r="J355" t="inlineStr"/>
       <c r="K355" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 22 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L355" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N355" s="1" t="n">
-        <v>46099</v>
+        <v>46092</v>
       </c>
     </row>
     <row r="356">
@@ -20332,21 +20470,21 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
+          <t>Frontier AI Benchmarking Datasets</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2424/overview/e618b7a8-ab7f-45f3-a098-57c01b334fcd</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-03-24 10:47</t>
+          <t>2026-03-23 10:49</t>
         </is>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46105.44930555556</v>
+        <v>46104.45069444444</v>
       </c>
       <c r="F356" t="b">
         <v>1</v>
@@ -20359,11 +20497,11 @@
       <c r="J356" t="inlineStr"/>
       <c r="K356" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L356" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M356" t="inlineStr">
         <is>
@@ -20382,12 +20520,12 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
+          <t>Medicines Manufacturing: Labs of the Future</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2417/overview/5ec76f19-8bd0-4dfa-b869-f4f0401448de</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -20409,15 +20547,15 @@
       <c r="J357" t="inlineStr"/>
       <c r="K357" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L357" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N357" s="1" t="n">
@@ -20432,21 +20570,21 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Industrial Research</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2428/overview/85fd40be-646f-4b95-8a12-f881334d871d</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F358" t="b">
         <v>1</v>
@@ -20459,19 +20597,19 @@
       <c r="J358" t="inlineStr"/>
       <c r="K358" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L358" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£750,000</t>
         </is>
       </c>
       <c r="N358" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="359">
@@ -20482,21 +20620,21 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
+          <t>AgriScale - Accelerating Agri-tech manufacturing: Experimental Development</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2427/overview/cb071e4d-3a72-4d77-9350-b2ae3d50a79f</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-03-26 10:49</t>
+          <t>2026-03-24 10:47</t>
         </is>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46107.45069444444</v>
+        <v>46105.44930555556</v>
       </c>
       <c r="F359" t="b">
         <v>1</v>
@@ -20509,19 +20647,19 @@
       <c r="J359" t="inlineStr"/>
       <c r="K359" t="inlineStr">
         <is>
-          <t>Wednesday 16 September 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L359" s="1" t="n">
-        <v>46281.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>£60.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N359" s="1" t="n">
-        <v>46106</v>
+        <v>46099</v>
       </c>
     </row>
     <row r="360">
@@ -20532,12 +20670,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Energy Efficiency</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2436/overview/97d03e1a-7760-4939-97b4-4f230c84a6aa</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -20582,21 +20720,21 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Electric Power</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2435/overview/592ea5c1-f713-4654-bb5e-d6894cd06d86</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-03-27 10:43</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46108.44652777778</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F361" t="b">
         <v>1</v>
@@ -20609,15 +20747,15 @@
       <c r="J361" t="inlineStr"/>
       <c r="K361" t="inlineStr">
         <is>
-          <t>Wednesday 1 April 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L361" s="1" t="n">
-        <v>46113.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N361" s="1" t="n">
@@ -20632,21 +20770,21 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
+          <t>Zero Emission Vessels and Infrastructure 2: Alternative Fuels</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2434/overview/f4a8b70b-ff7f-4943-9c8a-76c212b445a8</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-03-28 10:27</t>
+          <t>2026-03-26 10:49</t>
         </is>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46109.43541666667</v>
+        <v>46107.45069444444</v>
       </c>
       <c r="F362" t="b">
         <v>1</v>
@@ -20659,15 +20797,15 @@
       <c r="J362" t="inlineStr"/>
       <c r="K362" t="inlineStr">
         <is>
-          <t>Friday 29 May 2026 11:00am</t>
+          <t>Wednesday 16 September 2026 11:00am</t>
         </is>
       </c>
       <c r="L362" s="1" t="n">
-        <v>46171.45833333334</v>
+        <v>46281.45833333334</v>
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>£14.0 million</t>
+          <t>£60.0 million</t>
         </is>
       </c>
       <c r="N362" s="1" t="n">
@@ -20682,21 +20820,21 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: industrial research</t>
+          <t>Semiconductors and components for smart electronic platforms: applications with academic partners</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2441/overview/5ad05ad0-9f9a-47b7-8660-085608a668e0</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-27 10:43</t>
         </is>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46108.44652777778</v>
       </c>
       <c r="F363" t="b">
         <v>1</v>
@@ -20709,19 +20847,19 @@
       <c r="J363" t="inlineStr"/>
       <c r="K363" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Wednesday 1 April 2026 11:00am</t>
         </is>
       </c>
       <c r="L363" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46113.45833333334</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>£1.5 million</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N363" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="364">
@@ -20732,21 +20870,21 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Future offshore wind technologies: feasibility studies</t>
+          <t>Contracts for Innovation: ProQure - Scaling UK Quantum Computing</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2439/overview/06423ffe-b763-4cac-b83b-f80208dfe2f2</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-04-01 10:50</t>
+          <t>2026-03-28 10:27</t>
         </is>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46113.45138888889</v>
+        <v>46109.43541666667</v>
       </c>
       <c r="F364" t="b">
         <v>1</v>
@@ -20759,19 +20897,19 @@
       <c r="J364" t="inlineStr"/>
       <c r="K364" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
+          <t>Friday 29 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L364" s="1" t="n">
-        <v>46176.45833333334</v>
+        <v>46171.45833333334</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>£250,000</t>
+          <t>£14.0 million</t>
         </is>
       </c>
       <c r="N364" s="1" t="n">
-        <v>46113</v>
+        <v>46106</v>
       </c>
     </row>
     <row r="365">
@@ -20782,12 +20920,12 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Solution Development for Advanced Connectivity Technologies</t>
+          <t>Future offshore wind technologies: industrial research</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2433/overview/4458acff-f0d2-4e2d-836c-c151ebd82a1d</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -20809,15 +20947,15 @@
       <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr">
         <is>
-          <t>Wednesday 13 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L365" s="1" t="n">
-        <v>46155.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>£5.0 million</t>
+          <t>£1.5 million</t>
         </is>
       </c>
       <c r="N365" s="1" t="n">
@@ -20832,12 +20970,12 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
+          <t>Future offshore wind technologies: feasibility studies</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2432/overview/49f165f4-40af-4d16-8986-ba241fd2741a</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -20867,7 +21005,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>£2.0 million</t>
+          <t>£250,000</t>
         </is>
       </c>
       <c r="N366" s="1" t="n">
@@ -20882,21 +21020,21 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
+          <t>Solution Development for Advanced Connectivity Technologies</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2420/overview/00926b83-c904-4919-b7d0-2be6e12269a0</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-04-07 10:51</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46119.45208333333</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F367" t="b">
         <v>1</v>
@@ -20909,15 +21047,15 @@
       <c r="J367" t="inlineStr"/>
       <c r="K367" t="inlineStr">
         <is>
-          <t>Wednesday 20 May 2026 11:00am</t>
+          <t>Wednesday 13 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L367" s="1" t="n">
-        <v>46162.45833333334</v>
+        <v>46155.45833333334</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>£3.0 million</t>
+          <t>£5.0 million</t>
         </is>
       </c>
       <c r="N367" s="1" t="n">
@@ -20932,21 +21070,21 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Full ADOPT Grant: Round 7</t>
+          <t>CfI: Advanced Connectivity Technologies (ACT) – Call 1</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2437/overview/1123379f-9949-4cf0-acce-df748923a207</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-04-09 10:54</t>
+          <t>2026-04-01 10:50</t>
         </is>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46121.45416666667</v>
+        <v>46113.45138888889</v>
       </c>
       <c r="F368" t="b">
         <v>1</v>
@@ -20967,11 +21105,11 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>£100,000</t>
+          <t>£2.0 million</t>
         </is>
       </c>
       <c r="N368" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="369">
@@ -20982,21 +21120,21 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>DRIVE35 Scale-up Fund</t>
+          <t>Contracts for Innovation: Enabling Commercial Quantum Networking</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2426/overview/4766704a-4888-49f8-b4f3-1e370e9ee0c5</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-04-11 10:30</t>
+          <t>2026-04-07 10:51</t>
         </is>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46123.4375</v>
+        <v>46119.45208333333</v>
       </c>
       <c r="F369" t="b">
         <v>1</v>
@@ -21009,17 +21147,19 @@
       <c r="J369" t="inlineStr"/>
       <c r="K369" t="inlineStr">
         <is>
-          <t>Wednesday 1 July 2026 12:00pm</t>
-        </is>
-      </c>
-      <c r="L369" t="inlineStr"/>
+          <t>Wednesday 20 May 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L369" s="1" t="n">
+        <v>46162.45833333334</v>
+      </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>£20.0 million</t>
+          <t>£3.0 million</t>
         </is>
       </c>
       <c r="N369" s="1" t="n">
-        <v>46120</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="370">
@@ -21030,21 +21170,21 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Battery innovation feasibility studies round 2</t>
+          <t>Full ADOPT Grant: Round 7</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2442/overview/b9c07f24-e02d-4495-8351-0ed24aa9668d</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-09 10:54</t>
         </is>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46121.45416666667</v>
       </c>
       <c r="F370" t="b">
         <v>1</v>
@@ -21057,15 +21197,15 @@
       <c r="J370" t="inlineStr"/>
       <c r="K370" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
+          <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
       <c r="L370" s="1" t="n">
-        <v>46169.45833333334</v>
+        <v>46176.45833333334</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>£500,000</t>
+          <t>£100,000</t>
         </is>
       </c>
       <c r="N370" s="1" t="n">
@@ -21080,21 +21220,21 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Battery innovation concept development round 2</t>
+          <t>DRIVE35 Scale-up Fund</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2279/overview/029bd996-9abd-42d9-8134-e2d34e3cfff5</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-04-14 10:58</t>
+          <t>2026-04-11 10:30</t>
         </is>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46126.45694444444</v>
+        <v>46123.4375</v>
       </c>
       <c r="F371" t="b">
         <v>1</v>
@@ -21107,15 +21247,13 @@
       <c r="J371" t="inlineStr"/>
       <c r="K371" t="inlineStr">
         <is>
-          <t>Wednesday 27 May 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L371" s="1" t="n">
-        <v>46169.45833333334</v>
-      </c>
+          <t>Wednesday 1 July 2026 12:00pm</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr"/>
       <c r="M371" t="inlineStr">
         <is>
-          <t>£4.0 million</t>
+          <t>£20.0 million</t>
         </is>
       </c>
       <c r="N371" s="1" t="n">
@@ -21130,21 +21268,21 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>ADOPT Facilitator Support Grant: Round 8</t>
+          <t>Battery innovation feasibility studies round 2</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2444/overview/b355177a-c85f-4cd6-b5b5-c4836d09df3e</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-04-15 10:55</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46127.45486111111</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F372" t="b">
         <v>1</v>
@@ -21165,11 +21303,11 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>£2,500</t>
+          <t>£500,000</t>
         </is>
       </c>
       <c r="N372" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="373">
@@ -21180,21 +21318,21 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
+          <t>Battery innovation concept development round 2</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2443/overview/adca814a-3966-4fbb-afbe-a2ccbd4c3bae</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-04-18 10:35</t>
+          <t>2026-04-14 10:58</t>
         </is>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46130.44097222222</v>
+        <v>46126.45694444444</v>
       </c>
       <c r="F373" t="b">
         <v>1</v>
@@ -21207,19 +21345,19 @@
       <c r="J373" t="inlineStr"/>
       <c r="K373" t="inlineStr">
         <is>
-          <t>Wednesday 8 July 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L373" s="1" t="n">
-        <v>46211.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>£50,000</t>
+          <t>£4.0 million</t>
         </is>
       </c>
       <c r="N373" s="1" t="n">
-        <v>46127</v>
+        <v>46120</v>
       </c>
     </row>
     <row r="374">
@@ -21230,21 +21368,21 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
+          <t>ADOPT Facilitator Support Grant: Round 8</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2440/overview/630d8177-1633-413b-8c56-ad3fdcc8af82</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-04-20 11:16</t>
+          <t>2026-04-15 10:55</t>
         </is>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46132.46944444445</v>
+        <v>46127.45486111111</v>
       </c>
       <c r="F374" t="b">
         <v>1</v>
@@ -21257,15 +21395,15 @@
       <c r="J374" t="inlineStr"/>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Wednesday 24 June 2026 11:00am</t>
+          <t>Wednesday 27 May 2026 11:00am</t>
         </is>
       </c>
       <c r="L374" s="1" t="n">
-        <v>46197.45833333334</v>
+        <v>46169.45833333334</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>£8,500</t>
+          <t>£2,500</t>
         </is>
       </c>
       <c r="N374" s="1" t="n">
@@ -21280,21 +21418,21 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Advanced manufacturing supply chain innovation: CRD</t>
+          <t>Growth Cohorts: Next generation low carbon concrete cohort entry</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2450/overview/261cbeea-5b87-4730-9fe9-4d04acc3725f</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-04-21 11:02</t>
+          <t>2026-04-18 10:35</t>
         </is>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46133.45972222222</v>
+        <v>46130.44097222222</v>
       </c>
       <c r="F375" t="b">
         <v>1</v>
@@ -21307,15 +21445,15 @@
       <c r="J375" t="inlineStr"/>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Wednesday 10 June 2026 11:00am</t>
+          <t>Wednesday 8 July 2026 11:00am</t>
         </is>
       </c>
       <c r="L375" s="1" t="n">
-        <v>46183.45833333334</v>
+        <v>46211.45833333334</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>£1.0 million</t>
+          <t>£50,000</t>
         </is>
       </c>
       <c r="N375" s="1" t="n">
@@ -21330,21 +21468,21 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
+          <t>Knowledge Transfer Partnership (KTP): 2026 – 2027 Round 2</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2398/overview/318a8834-930f-4577-9069-26459a0def93</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-04-22 11:00</t>
+          <t>2026-04-20 11:16</t>
         </is>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46134.45833333334</v>
+        <v>46132.46944444445</v>
       </c>
       <c r="F376" t="b">
         <v>1</v>
@@ -21357,13 +21495,19 @@
       <c r="J376" t="inlineStr"/>
       <c r="K376" t="inlineStr">
         <is>
-          <t>There is no submission deadline</t>
-        </is>
-      </c>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
+          <t>Wednesday 24 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L376" s="1" t="n">
+        <v>46197.45833333334</v>
+      </c>
+      <c r="M376" t="inlineStr">
+        <is>
+          <t>£8,500</t>
+        </is>
+      </c>
       <c r="N376" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="377">
@@ -21374,21 +21518,21 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
+          <t>Advanced manufacturing supply chain innovation: CRD</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2453/overview/79b9483b-140e-44e9-86af-db7792c594d2</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-04-23 11:03</t>
+          <t>2026-04-21 11:02</t>
         </is>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46135.46041666667</v>
+        <v>46133.45972222222</v>
       </c>
       <c r="F377" t="b">
         <v>1</v>
@@ -21409,11 +21553,11 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>£300,000</t>
+          <t>£1.0 million</t>
         </is>
       </c>
       <c r="N377" s="1" t="n">
-        <v>46134</v>
+        <v>46127</v>
       </c>
     </row>
     <row r="378">
@@ -21424,21 +21568,21 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Dual-use aviation systems and autonomy</t>
+          <t>Innovate UK Venture Builder Pilot Expression of Interest</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2457/overview/343a1d9f-29cb-4184-96bc-565bcfd09462</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-22 11:00</t>
         </is>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46134.45833333334</v>
       </c>
       <c r="F378" t="b">
         <v>1</v>
@@ -21451,17 +21595,11 @@
       <c r="J378" t="inlineStr"/>
       <c r="K378" t="inlineStr">
         <is>
-          <t>Wednesday 3 June 2026 11:00am</t>
-        </is>
-      </c>
-      <c r="L378" s="1" t="n">
-        <v>46176.45833333334</v>
-      </c>
-      <c r="M378" t="inlineStr">
-        <is>
-          <t>£1.2 million</t>
-        </is>
-      </c>
+          <t>There is no submission deadline</t>
+        </is>
+      </c>
+      <c r="L378" t="inlineStr"/>
+      <c r="M378" t="inlineStr"/>
       <c r="N378" s="1" t="n">
         <v>46134</v>
       </c>
@@ -21474,21 +21612,21 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Counter UAS Technologies</t>
+          <t>Contracts for Innovation: Cyber scale in critical sectors</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2452/overview/df0addbf-9146-4b7f-b8b5-e78470917675</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-04-28 11:42</t>
+          <t>2026-04-23 11:03</t>
         </is>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46140.4875</v>
+        <v>46135.46041666667</v>
       </c>
       <c r="F379" t="b">
         <v>1</v>
@@ -21501,18 +21639,118 @@
       <c r="J379" t="inlineStr"/>
       <c r="K379" t="inlineStr">
         <is>
+          <t>Wednesday 10 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L379" s="1" t="n">
+        <v>46183.45833333334</v>
+      </c>
+      <c r="M379" t="inlineStr">
+        <is>
+          <t>£300,000</t>
+        </is>
+      </c>
+      <c r="N379" s="1" t="n">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>Dual-use aviation systems and autonomy</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2467/overview/3ac02a1d-68e5-460b-bddb-0ecacdabfb00</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:42</t>
+        </is>
+      </c>
+      <c r="E380" s="1" t="n">
+        <v>46140.4875</v>
+      </c>
+      <c r="F380" t="b">
+        <v>1</v>
+      </c>
+      <c r="G380" t="inlineStr"/>
+      <c r="H380" t="b">
+        <v>0</v>
+      </c>
+      <c r="I380" t="inlineStr"/>
+      <c r="J380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
           <t>Wednesday 3 June 2026 11:00am</t>
         </is>
       </c>
-      <c r="L379" s="1" t="n">
+      <c r="L380" s="1" t="n">
         <v>46176.45833333334</v>
       </c>
-      <c r="M379" t="inlineStr">
+      <c r="M380" t="inlineStr">
         <is>
           <t>£1.2 million</t>
         </is>
       </c>
-      <c r="N379" s="1" t="n">
+      <c r="N380" s="1" t="n">
+        <v>46134</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Innovate Funding Service</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Counter UAS Technologies</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://apply-for-innovation-funding.service.gov.uk/competition/2468/overview/6be7375d-717c-49b4-9411-f7709bb9e6ea</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-04-28 11:42</t>
+        </is>
+      </c>
+      <c r="E381" s="1" t="n">
+        <v>46140.4875</v>
+      </c>
+      <c r="F381" t="b">
+        <v>1</v>
+      </c>
+      <c r="G381" t="inlineStr"/>
+      <c r="H381" t="b">
+        <v>0</v>
+      </c>
+      <c r="I381" t="inlineStr"/>
+      <c r="J381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Wednesday 3 June 2026 11:00am</t>
+        </is>
+      </c>
+      <c r="L381" s="1" t="n">
+        <v>46176.45833333334</v>
+      </c>
+      <c r="M381" t="inlineStr">
+        <is>
+          <t>£1.2 million</t>
+        </is>
+      </c>
+      <c r="N381" s="1" t="n">
         <v>46134</v>
       </c>
     </row>
@@ -21554,10 +21792,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C2" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="3">
@@ -21580,10 +21818,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="5">
